--- a/MCA_Revenue_Demand_Generation_Report.xlsx
+++ b/MCA_Revenue_Demand_Generation_Report.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c734cc42baaaa4a/Documents/GitHub/Cross_Department_Demand_Revenue_Tracker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ICCLEA~1\AppData\Local\Temp\claude\c--Users-IC-Clearwater-OneDrive-Documents-GitHub-Demand-Revenue-Insights-Console\d9369524-f00a-44d4-8087-4ed1242079d6\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_0EF3AFAE11440061DAF3D29CC181A74C76CB9137" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{043879F7-19AF-4D56-9933-BDB6755E4922}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A82065-9B93-4A8A-B33F-4386A43754B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MAIN DASHBOARD" sheetId="2" r:id="rId1"/>
-    <sheet name="Analysis Dashboard" sheetId="3" r:id="rId2"/>
-    <sheet name="Demand_Input" sheetId="6" r:id="rId3"/>
-    <sheet name="Revenue_Input" sheetId="7" r:id="rId4"/>
-    <sheet name="Analysis_Calc" sheetId="4" r:id="rId5"/>
-    <sheet name="Calculations" sheetId="5" r:id="rId6"/>
-    <sheet name="Lists" sheetId="8" r:id="rId7"/>
+    <sheet name="ReadMe" sheetId="9" r:id="rId1"/>
+    <sheet name="MAIN DASHBOARD" sheetId="2" r:id="rId2"/>
+    <sheet name="Analysis Dashboard" sheetId="3" r:id="rId3"/>
+    <sheet name="Demand_Input" sheetId="6" r:id="rId4"/>
+    <sheet name="Revenue_Input" sheetId="7" r:id="rId5"/>
+    <sheet name="Analysis_Calc" sheetId="4" r:id="rId6"/>
+    <sheet name="Calculations" sheetId="5" r:id="rId7"/>
+    <sheet name="Lists" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="DemandGroups">Lists!$A$4:$A$7</definedName>
     <definedName name="DemandStreams">Lists!$B$4:$B$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MAIN DASHBOARD'!$A$1:$L$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'MAIN DASHBOARD'!$A$1:$L$32</definedName>
     <definedName name="RevenueGroups">Lists!$D$4:$D$7</definedName>
     <definedName name="RevenueStreams">Lists!$E$4:$E$7</definedName>
   </definedNames>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="152">
   <si>
     <t>Monthly</t>
   </si>
@@ -328,6 +329,180 @@
   </si>
   <si>
     <t>Each business group reports under exactly one campaign/stream (same row above).</t>
+  </si>
+  <si>
+    <t>Demand &amp; Revenue Insights Console</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Corporate Affairs</t>
+  </si>
+  <si>
+    <t>Every team enters one row per day. Every total, percentage, chart and KPI tile on the two dashboards is calculated from those rows. Nobody edits a formula during normal use.</t>
+  </si>
+  <si>
+    <t>Tab colours</t>
+  </si>
+  <si>
+    <t>Green tabs are for typing. Blue tabs are for reading. Grey tabs are never edited.</t>
+  </si>
+  <si>
+    <t>The sheets</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>What it is</t>
+  </si>
+  <si>
+    <t>ReadMe</t>
+  </si>
+  <si>
+    <t>grey</t>
+  </si>
+  <si>
+    <t>This page</t>
+  </si>
+  <si>
+    <t>MAIN DASHBOARD</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>Month, quarter and year to date, with movement percentages</t>
+  </si>
+  <si>
+    <t>Analysis Dashboard</t>
+  </si>
+  <si>
+    <t>KPI tiles, trends and contribution</t>
+  </si>
+  <si>
+    <t>Demand_Input</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>Daily leads</t>
+  </si>
+  <si>
+    <t>Revenue_Input</t>
+  </si>
+  <si>
+    <t>Daily revenue, in Rands</t>
+  </si>
+  <si>
+    <t>Calculations</t>
+  </si>
+  <si>
+    <t>Engine behind MAIN DASHBOARD</t>
+  </si>
+  <si>
+    <t>Analysis_Calc</t>
+  </si>
+  <si>
+    <t>Engine behind Analysis Dashboard</t>
+  </si>
+  <si>
+    <t>Lists</t>
+  </si>
+  <si>
+    <t>Approved values that drive the drop-downs</t>
+  </si>
+  <si>
+    <t>Adding a row</t>
+  </si>
+  <si>
+    <t>1.  Open Demand_Input for leads, or Revenue_Input for revenue.</t>
+  </si>
+  <si>
+    <t>2.  Go to the first empty row at the bottom of the table and type the date in column A.</t>
+  </si>
+  <si>
+    <t>3.  Choose the Business Group in column B from the drop-down. A value that is not on the list is rejected.</t>
+  </si>
+  <si>
+    <t>4.  Choose the Campaign/Stream in column C. Each business group reports under exactly one stream.</t>
+  </si>
+  <si>
+    <t>5.  Enter the day's figure in column D. Negative values are rejected.</t>
+  </si>
+  <si>
+    <t>If a team reported nothing on a day, leave the row out. Missing days count as zero and break nothing.</t>
+  </si>
+  <si>
+    <t>Rules that keep this working</t>
+  </si>
+  <si>
+    <t>Do not rename sheets, the DemandTbl or RevenueTbl tables, or any column heading, because formulas reference them by name.</t>
+  </si>
+  <si>
+    <t>Do not insert rows anywhere except the bottom of the input tables.</t>
+  </si>
+  <si>
+    <t>Do not type into grey tabs. If a number looks wrong, the cause is in the input rows.</t>
+  </si>
+  <si>
+    <t>Adding a business group or campaign is a structural change for the workbook owner only.</t>
+  </si>
+  <si>
+    <t>If something looks wrong</t>
+  </si>
+  <si>
+    <t>Symptom</t>
+  </si>
+  <si>
+    <t>Cause</t>
+  </si>
+  <si>
+    <t>Fix</t>
+  </si>
+  <si>
+    <t>A group shows 0 for a period that has data</t>
+  </si>
+  <si>
+    <t>The Business Group text does not exactly match the approved value</t>
+  </si>
+  <si>
+    <t>Re-select it from the drop-down</t>
+  </si>
+  <si>
+    <t>A percentage is blank</t>
+  </si>
+  <si>
+    <t>The previous period had no data, so there is nothing to compare</t>
+  </si>
+  <si>
+    <t>Intentional, nothing to fix</t>
+  </si>
+  <si>
+    <t>An entry is rejected</t>
+  </si>
+  <si>
+    <t>The value is not on the approved list, is negative, or is not a valid date</t>
+  </si>
+  <si>
+    <t>Correct it. Approved values are on Lists</t>
+  </si>
+  <si>
+    <t>Charts show months with no line</t>
+  </si>
+  <si>
+    <t>Those months are in the future</t>
+  </si>
+  <si>
+    <t>Numbers look stale</t>
+  </si>
+  <si>
+    <t>The workbook has not recalculated</t>
+  </si>
+  <si>
+    <t>Press F9, or close and reopen</t>
   </si>
 </sst>
 </file>
@@ -342,9 +517,9 @@
     <numFmt numFmtId="168" formatCode="&quot;R&quot;\ #,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="&quot;R&quot;\ #,##0.00"/>
-    <numFmt numFmtId="174" formatCode="[$R-1C09]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,8 +699,43 @@
       <color rgb="FF898781"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF1F3E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6B6B6B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF6B6B6B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,8 +787,14 @@
         <fgColor rgb="FFF0EFEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -704,11 +920,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2A78D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -812,30 +1037,31 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -859,15 +1085,27 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <numFmt numFmtId="174" formatCode="[$R-1C09]#,##0.00"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF888888"/>
@@ -951,6 +1189,9 @@
         <name val="Calibri"/>
         <charset val="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$R-1C09]#,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3593,7 +3834,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Business Group"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Campaign/Stream"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Daily Revenue (R)" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Daily Revenue (R)" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3777,6 +4018,327 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E480212-EDE8-48F9-A5BC-1FD92D832AD3}">
+  <sheetPr>
+    <tabColor rgb="FF898781"/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="73" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="75" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="75" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="75" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="76" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="75"/>
+      <c r="C33" s="75"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="76" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="79" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="79" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="79" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A4:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2A78D6"/>
@@ -3797,72 +4359,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="str">
+      <c r="A1" s="61" t="str">
         <f ca="1">TEXT(TODAY(),"mmmm")</f>
         <v>July</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
     </row>
     <row r="2" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="E2" s="61" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="E2" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="56"/>
-      <c r="H2" s="61" t="s">
+      <c r="F2" s="57"/>
+      <c r="H2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="K2" s="61" t="s">
+      <c r="I2" s="57"/>
+      <c r="K2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="56"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="E3" s="60" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="E3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="H3" s="60" t="s">
+      <c r="F3" s="57"/>
+      <c r="H3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="56"/>
-      <c r="K3" s="60" t="s">
+      <c r="I3" s="57"/>
+      <c r="K3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="56"/>
+      <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="56"/>
+      <c r="C5" s="57"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="E6" s="58" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="E6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="F6" s="58"/>
+      <c r="H6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="K6" s="58" t="s">
+      <c r="I6" s="58"/>
+      <c r="K6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="59"/>
+      <c r="L6" s="58"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="62" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -3891,7 +4453,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56"/>
+      <c r="A8" s="57"/>
       <c r="B8" s="11" t="str">
         <f>Calculations!A14</f>
         <v>JSE SheInvests</v>
@@ -3920,7 +4482,7 @@
         <f ca="1">Calculations!I14</f>
         <v>986</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="59">
         <f ca="1">Calculations!I18</f>
         <v>4261</v>
       </c>
@@ -3954,7 +4516,7 @@
         <f ca="1">Calculations!I15</f>
         <v>1075</v>
       </c>
-      <c r="L9" s="56"/>
+      <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
@@ -3985,7 +4547,7 @@
         <f ca="1">Calculations!I16</f>
         <v>1112</v>
       </c>
-      <c r="L10" s="56"/>
+      <c r="L10" s="57"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="str">
@@ -4016,7 +4578,7 @@
         <f ca="1">Calculations!I17</f>
         <v>1088</v>
       </c>
-      <c r="L11" s="59"/>
+      <c r="L11" s="58"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
@@ -4025,29 +4587,29 @@
       <c r="J12" s="23"/>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="56"/>
+      <c r="C13" s="57"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="E14" s="58" t="s">
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="E14" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="H14" s="58" t="s">
+      <c r="F14" s="58"/>
+      <c r="H14" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="59"/>
-      <c r="K14" s="58" t="s">
+      <c r="I14" s="58"/>
+      <c r="K14" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="59"/>
+      <c r="L14" s="58"/>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="62" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -4076,7 +4638,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56"/>
+      <c r="A16" s="57"/>
       <c r="B16" s="24" t="str">
         <f>Calculations!A23</f>
         <v>Primary Markets</v>
@@ -4105,7 +4667,7 @@
         <f ca="1">Calculations!I23</f>
         <v>48560</v>
       </c>
-      <c r="L16" s="63">
+      <c r="L16" s="65">
         <f ca="1">Calculations!I27</f>
         <v>227195</v>
       </c>
@@ -4139,7 +4701,7 @@
         <f ca="1">Calculations!I24</f>
         <v>65304</v>
       </c>
-      <c r="L17" s="56"/>
+      <c r="L17" s="57"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="str">
@@ -4170,7 +4732,7 @@
         <f ca="1">Calculations!I25</f>
         <v>59335</v>
       </c>
-      <c r="L18" s="56"/>
+      <c r="L18" s="57"/>
     </row>
     <row r="19" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="str">
@@ -4201,7 +4763,7 @@
         <f ca="1">Calculations!I26</f>
         <v>53996</v>
       </c>
-      <c r="L19" s="59"/>
+      <c r="L19" s="58"/>
     </row>
     <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="52" t="s">
@@ -4279,6 +4841,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="L8:L11"/>
     <mergeCell ref="E6:F6"/>
@@ -4295,51 +4860,48 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="B13:C14"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="L16:L19"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F11">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F19">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I11">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I19">
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4348,7 +4910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2A78D6"/>
@@ -4372,55 +4934,55 @@
       </c>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="E4" s="65" t="s">
+      <c r="C4" s="57"/>
+      <c r="E4" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="H4" s="65" t="s">
+      <c r="F4" s="57"/>
+      <c r="H4" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="56"/>
-      <c r="K4" s="65" t="s">
+      <c r="I4" s="57"/>
+      <c r="K4" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="56"/>
-      <c r="N4" s="71" t="s">
+      <c r="L4" s="57"/>
+      <c r="N4" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66">
+      <c r="B5" s="67">
         <f ca="1">Analysis_Calc!B33</f>
         <v>4261</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="E5" s="67">
+      <c r="C5" s="57"/>
+      <c r="E5" s="68">
         <f ca="1">Analysis_Calc!B34</f>
         <v>227195</v>
       </c>
-      <c r="F5" s="56"/>
-      <c r="H5" s="70">
+      <c r="F5" s="57"/>
+      <c r="H5" s="71">
         <f ca="1">Analysis_Calc!B35</f>
         <v>53.319643276226238</v>
       </c>
-      <c r="I5" s="56"/>
-      <c r="K5" s="68" t="str">
+      <c r="I5" s="57"/>
+      <c r="K5" s="69" t="str">
         <f ca="1">Analysis_Calc!B36</f>
         <v>May</v>
       </c>
-      <c r="L5" s="56"/>
-      <c r="N5" s="69" t="str">
+      <c r="L5" s="57"/>
+      <c r="N5" s="70" t="str">
         <f ca="1">Analysis_Calc!B37</f>
         <v>Secondary Markets</v>
       </c>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
     </row>
     <row r="62" spans="2:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="46"/>
@@ -4491,7 +5053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF008300"/>
@@ -7314,7 +7876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF008300"/>
@@ -7352,7 +7914,7 @@
       <c r="C2" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="72">
+      <c r="D2" s="55">
         <v>116</v>
       </c>
     </row>
@@ -7366,7 +7928,7 @@
       <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="72">
+      <c r="D3" s="55">
         <v>513</v>
       </c>
     </row>
@@ -7380,7 +7942,7 @@
       <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="55">
         <v>1122</v>
       </c>
     </row>
@@ -7394,7 +7956,7 @@
       <c r="C5" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="55">
         <v>2482</v>
       </c>
     </row>
@@ -7408,7 +7970,7 @@
       <c r="C6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="55">
         <v>2280</v>
       </c>
     </row>
@@ -7422,7 +7984,7 @@
       <c r="C7" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="55">
         <v>107</v>
       </c>
     </row>
@@ -7436,7 +7998,7 @@
       <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="55">
         <v>798</v>
       </c>
     </row>
@@ -7450,7 +8012,7 @@
       <c r="C9" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="55">
         <v>476</v>
       </c>
     </row>
@@ -7464,7 +8026,7 @@
       <c r="C10" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="55">
         <v>1630</v>
       </c>
     </row>
@@ -7478,7 +8040,7 @@
       <c r="C11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="55">
         <v>2130</v>
       </c>
     </row>
@@ -7492,7 +8054,7 @@
       <c r="C12" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="55">
         <v>1128</v>
       </c>
     </row>
@@ -7506,7 +8068,7 @@
       <c r="C13" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="55">
         <v>221</v>
       </c>
     </row>
@@ -7520,7 +8082,7 @@
       <c r="C14" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="55">
         <v>152</v>
       </c>
     </row>
@@ -7534,7 +8096,7 @@
       <c r="C15" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="55">
         <v>1050</v>
       </c>
     </row>
@@ -7548,7 +8110,7 @@
       <c r="C16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="72">
+      <c r="D16" s="55">
         <v>2138</v>
       </c>
     </row>
@@ -7562,7 +8124,7 @@
       <c r="C17" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="55">
         <v>777</v>
       </c>
     </row>
@@ -7576,7 +8138,7 @@
       <c r="C18" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="55">
         <v>1550</v>
       </c>
     </row>
@@ -7590,7 +8152,7 @@
       <c r="C19" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="55">
         <v>123</v>
       </c>
     </row>
@@ -7604,7 +8166,7 @@
       <c r="C20" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="55">
         <v>2459</v>
       </c>
     </row>
@@ -7618,7 +8180,7 @@
       <c r="C21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="72">
+      <c r="D21" s="55">
         <v>2183</v>
       </c>
     </row>
@@ -7632,7 +8194,7 @@
       <c r="C22" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="72">
+      <c r="D22" s="55">
         <v>390</v>
       </c>
     </row>
@@ -7646,7 +8208,7 @@
       <c r="C23" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="72">
+      <c r="D23" s="55">
         <v>1788</v>
       </c>
     </row>
@@ -7660,7 +8222,7 @@
       <c r="C24" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="55">
         <v>826</v>
       </c>
     </row>
@@ -7674,7 +8236,7 @@
       <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="72">
+      <c r="D25" s="55">
         <v>1661</v>
       </c>
     </row>
@@ -7688,7 +8250,7 @@
       <c r="C26" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="55">
         <v>1899</v>
       </c>
     </row>
@@ -7702,7 +8264,7 @@
       <c r="C27" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="55">
         <v>2258</v>
       </c>
     </row>
@@ -7716,7 +8278,7 @@
       <c r="C28" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="72">
+      <c r="D28" s="55">
         <v>752</v>
       </c>
     </row>
@@ -7730,7 +8292,7 @@
       <c r="C29" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="72">
+      <c r="D29" s="55">
         <v>1483</v>
       </c>
     </row>
@@ -7744,7 +8306,7 @@
       <c r="C30" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="72">
+      <c r="D30" s="55">
         <v>277</v>
       </c>
     </row>
@@ -7758,7 +8320,7 @@
       <c r="C31" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="72">
+      <c r="D31" s="55">
         <v>845</v>
       </c>
     </row>
@@ -7772,7 +8334,7 @@
       <c r="C32" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="72">
+      <c r="D32" s="55">
         <v>818</v>
       </c>
     </row>
@@ -7786,7 +8348,7 @@
       <c r="C33" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="72">
+      <c r="D33" s="55">
         <v>624</v>
       </c>
     </row>
@@ -7800,7 +8362,7 @@
       <c r="C34" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="55">
         <v>511</v>
       </c>
     </row>
@@ -7814,7 +8376,7 @@
       <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="55">
         <v>2166</v>
       </c>
     </row>
@@ -7828,7 +8390,7 @@
       <c r="C36" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="55">
         <v>1184</v>
       </c>
     </row>
@@ -7842,7 +8404,7 @@
       <c r="C37" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="55">
         <v>289</v>
       </c>
     </row>
@@ -7856,7 +8418,7 @@
       <c r="C38" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="72">
+      <c r="D38" s="55">
         <v>473</v>
       </c>
     </row>
@@ -7870,7 +8432,7 @@
       <c r="C39" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="55">
         <v>2068</v>
       </c>
     </row>
@@ -7884,7 +8446,7 @@
       <c r="C40" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="72">
+      <c r="D40" s="55">
         <v>282</v>
       </c>
     </row>
@@ -7898,7 +8460,7 @@
       <c r="C41" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="72">
+      <c r="D41" s="55">
         <v>721</v>
       </c>
     </row>
@@ -7912,7 +8474,7 @@
       <c r="C42" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="72">
+      <c r="D42" s="55">
         <v>333</v>
       </c>
     </row>
@@ -7926,7 +8488,7 @@
       <c r="C43" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="72">
+      <c r="D43" s="55">
         <v>503</v>
       </c>
     </row>
@@ -7940,7 +8502,7 @@
       <c r="C44" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="72">
+      <c r="D44" s="55">
         <v>2013</v>
       </c>
     </row>
@@ -7954,7 +8516,7 @@
       <c r="C45" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="72">
+      <c r="D45" s="55">
         <v>1151</v>
       </c>
     </row>
@@ -7968,7 +8530,7 @@
       <c r="C46" t="s">
         <v>82</v>
       </c>
-      <c r="D46" s="72">
+      <c r="D46" s="55">
         <v>501</v>
       </c>
     </row>
@@ -7982,7 +8544,7 @@
       <c r="C47" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="72">
+      <c r="D47" s="55">
         <v>1567</v>
       </c>
     </row>
@@ -7996,7 +8558,7 @@
       <c r="C48" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="72">
+      <c r="D48" s="55">
         <v>2027</v>
       </c>
     </row>
@@ -8010,7 +8572,7 @@
       <c r="C49" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="72">
+      <c r="D49" s="55">
         <v>1737</v>
       </c>
     </row>
@@ -8024,7 +8586,7 @@
       <c r="C50" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="72">
+      <c r="D50" s="55">
         <v>1039</v>
       </c>
     </row>
@@ -8038,7 +8600,7 @@
       <c r="C51" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="72">
+      <c r="D51" s="55">
         <v>287</v>
       </c>
     </row>
@@ -8052,7 +8614,7 @@
       <c r="C52" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="72">
+      <c r="D52" s="55">
         <v>1325</v>
       </c>
     </row>
@@ -8066,7 +8628,7 @@
       <c r="C53" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="72">
+      <c r="D53" s="55">
         <v>2062</v>
       </c>
     </row>
@@ -8080,7 +8642,7 @@
       <c r="C54" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="72">
+      <c r="D54" s="55">
         <v>1166</v>
       </c>
     </row>
@@ -8094,7 +8656,7 @@
       <c r="C55" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="72">
+      <c r="D55" s="55">
         <v>2013</v>
       </c>
     </row>
@@ -8108,7 +8670,7 @@
       <c r="C56" t="s">
         <v>82</v>
       </c>
-      <c r="D56" s="72">
+      <c r="D56" s="55">
         <v>36</v>
       </c>
     </row>
@@ -8122,7 +8684,7 @@
       <c r="C57" t="s">
         <v>83</v>
       </c>
-      <c r="D57" s="72">
+      <c r="D57" s="55">
         <v>1875</v>
       </c>
     </row>
@@ -8136,7 +8698,7 @@
       <c r="C58" t="s">
         <v>81</v>
       </c>
-      <c r="D58" s="72">
+      <c r="D58" s="55">
         <v>2209</v>
       </c>
     </row>
@@ -8150,7 +8712,7 @@
       <c r="C59" t="s">
         <v>82</v>
       </c>
-      <c r="D59" s="72">
+      <c r="D59" s="55">
         <v>1474</v>
       </c>
     </row>
@@ -8164,7 +8726,7 @@
       <c r="C60" t="s">
         <v>83</v>
       </c>
-      <c r="D60" s="72">
+      <c r="D60" s="55">
         <v>57</v>
       </c>
     </row>
@@ -8178,7 +8740,7 @@
       <c r="C61" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="72">
+      <c r="D61" s="55">
         <v>2278</v>
       </c>
     </row>
@@ -8192,7 +8754,7 @@
       <c r="C62" t="s">
         <v>84</v>
       </c>
-      <c r="D62" s="72">
+      <c r="D62" s="55">
         <v>2120</v>
       </c>
     </row>
@@ -8206,7 +8768,7 @@
       <c r="C63" t="s">
         <v>81</v>
       </c>
-      <c r="D63" s="72">
+      <c r="D63" s="55">
         <v>1081</v>
       </c>
     </row>
@@ -8220,7 +8782,7 @@
       <c r="C64" t="s">
         <v>82</v>
       </c>
-      <c r="D64" s="72">
+      <c r="D64" s="55">
         <v>671</v>
       </c>
     </row>
@@ -8234,7 +8796,7 @@
       <c r="C65" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="72">
+      <c r="D65" s="55">
         <v>2108</v>
       </c>
     </row>
@@ -8248,7 +8810,7 @@
       <c r="C66" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="72">
+      <c r="D66" s="55">
         <v>2067</v>
       </c>
     </row>
@@ -8262,7 +8824,7 @@
       <c r="C67" t="s">
         <v>83</v>
       </c>
-      <c r="D67" s="72">
+      <c r="D67" s="55">
         <v>1681</v>
       </c>
     </row>
@@ -8276,7 +8838,7 @@
       <c r="C68" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="72">
+      <c r="D68" s="55">
         <v>337</v>
       </c>
     </row>
@@ -8290,7 +8852,7 @@
       <c r="C69" t="s">
         <v>81</v>
       </c>
-      <c r="D69" s="72">
+      <c r="D69" s="55">
         <v>2176</v>
       </c>
     </row>
@@ -8304,7 +8866,7 @@
       <c r="C70" t="s">
         <v>82</v>
       </c>
-      <c r="D70" s="72">
+      <c r="D70" s="55">
         <v>682</v>
       </c>
     </row>
@@ -8318,7 +8880,7 @@
       <c r="C71" t="s">
         <v>83</v>
       </c>
-      <c r="D71" s="72">
+      <c r="D71" s="55">
         <v>1575</v>
       </c>
     </row>
@@ -8332,7 +8894,7 @@
       <c r="C72" t="s">
         <v>84</v>
       </c>
-      <c r="D72" s="72">
+      <c r="D72" s="55">
         <v>242</v>
       </c>
     </row>
@@ -8346,7 +8908,7 @@
       <c r="C73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="72">
+      <c r="D73" s="55">
         <v>646</v>
       </c>
     </row>
@@ -8360,7 +8922,7 @@
       <c r="C74" t="s">
         <v>82</v>
       </c>
-      <c r="D74" s="72">
+      <c r="D74" s="55">
         <v>1502</v>
       </c>
     </row>
@@ -8374,7 +8936,7 @@
       <c r="C75" t="s">
         <v>81</v>
       </c>
-      <c r="D75" s="72">
+      <c r="D75" s="55">
         <v>109</v>
       </c>
     </row>
@@ -8388,7 +8950,7 @@
       <c r="C76" t="s">
         <v>82</v>
       </c>
-      <c r="D76" s="72">
+      <c r="D76" s="55">
         <v>2095</v>
       </c>
     </row>
@@ -8402,7 +8964,7 @@
       <c r="C77" t="s">
         <v>82</v>
       </c>
-      <c r="D77" s="72">
+      <c r="D77" s="55">
         <v>292</v>
       </c>
     </row>
@@ -8416,7 +8978,7 @@
       <c r="C78" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="72">
+      <c r="D78" s="55">
         <v>1261</v>
       </c>
     </row>
@@ -8430,7 +8992,7 @@
       <c r="C79" t="s">
         <v>83</v>
       </c>
-      <c r="D79" s="72">
+      <c r="D79" s="55">
         <v>2172</v>
       </c>
     </row>
@@ -8444,7 +9006,7 @@
       <c r="C80" t="s">
         <v>81</v>
       </c>
-      <c r="D80" s="72">
+      <c r="D80" s="55">
         <v>234</v>
       </c>
     </row>
@@ -8458,7 +9020,7 @@
       <c r="C81" t="s">
         <v>81</v>
       </c>
-      <c r="D81" s="72">
+      <c r="D81" s="55">
         <v>1172</v>
       </c>
     </row>
@@ -8472,7 +9034,7 @@
       <c r="C82" t="s">
         <v>82</v>
       </c>
-      <c r="D82" s="72">
+      <c r="D82" s="55">
         <v>1013</v>
       </c>
     </row>
@@ -8486,7 +9048,7 @@
       <c r="C83" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="72">
+      <c r="D83" s="55">
         <v>1308</v>
       </c>
     </row>
@@ -8500,7 +9062,7 @@
       <c r="C84" t="s">
         <v>84</v>
       </c>
-      <c r="D84" s="72">
+      <c r="D84" s="55">
         <v>117</v>
       </c>
     </row>
@@ -8514,7 +9076,7 @@
       <c r="C85" t="s">
         <v>82</v>
       </c>
-      <c r="D85" s="72">
+      <c r="D85" s="55">
         <v>1843</v>
       </c>
     </row>
@@ -8528,7 +9090,7 @@
       <c r="C86" t="s">
         <v>81</v>
       </c>
-      <c r="D86" s="72">
+      <c r="D86" s="55">
         <v>1185</v>
       </c>
     </row>
@@ -8542,7 +9104,7 @@
       <c r="C87" t="s">
         <v>82</v>
       </c>
-      <c r="D87" s="72">
+      <c r="D87" s="55">
         <v>1470</v>
       </c>
     </row>
@@ -8556,7 +9118,7 @@
       <c r="C88" t="s">
         <v>83</v>
       </c>
-      <c r="D88" s="72">
+      <c r="D88" s="55">
         <v>1672</v>
       </c>
     </row>
@@ -8570,7 +9132,7 @@
       <c r="C89" t="s">
         <v>84</v>
       </c>
-      <c r="D89" s="72">
+      <c r="D89" s="55">
         <v>2236</v>
       </c>
     </row>
@@ -8584,7 +9146,7 @@
       <c r="C90" t="s">
         <v>81</v>
       </c>
-      <c r="D90" s="72">
+      <c r="D90" s="55">
         <v>1554</v>
       </c>
     </row>
@@ -8598,7 +9160,7 @@
       <c r="C91" t="s">
         <v>83</v>
       </c>
-      <c r="D91" s="72">
+      <c r="D91" s="55">
         <v>1166</v>
       </c>
     </row>
@@ -8612,7 +9174,7 @@
       <c r="C92" t="s">
         <v>84</v>
       </c>
-      <c r="D92" s="72">
+      <c r="D92" s="55">
         <v>911</v>
       </c>
     </row>
@@ -8626,7 +9188,7 @@
       <c r="C93" t="s">
         <v>81</v>
       </c>
-      <c r="D93" s="72">
+      <c r="D93" s="55">
         <v>998</v>
       </c>
     </row>
@@ -8640,7 +9202,7 @@
       <c r="C94" t="s">
         <v>84</v>
       </c>
-      <c r="D94" s="72">
+      <c r="D94" s="55">
         <v>1073</v>
       </c>
     </row>
@@ -8654,7 +9216,7 @@
       <c r="C95" t="s">
         <v>83</v>
       </c>
-      <c r="D95" s="72">
+      <c r="D95" s="55">
         <v>1989</v>
       </c>
     </row>
@@ -8668,7 +9230,7 @@
       <c r="C96" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="72">
+      <c r="D96" s="55">
         <v>701</v>
       </c>
     </row>
@@ -8682,7 +9244,7 @@
       <c r="C97" t="s">
         <v>81</v>
       </c>
-      <c r="D97" s="72">
+      <c r="D97" s="55">
         <v>303</v>
       </c>
     </row>
@@ -8696,7 +9258,7 @@
       <c r="C98" t="s">
         <v>83</v>
       </c>
-      <c r="D98" s="72">
+      <c r="D98" s="55">
         <v>561</v>
       </c>
     </row>
@@ -8710,7 +9272,7 @@
       <c r="C99" t="s">
         <v>82</v>
       </c>
-      <c r="D99" s="72">
+      <c r="D99" s="55">
         <v>2226</v>
       </c>
     </row>
@@ -8724,7 +9286,7 @@
       <c r="C100" t="s">
         <v>83</v>
       </c>
-      <c r="D100" s="72">
+      <c r="D100" s="55">
         <v>1899</v>
       </c>
     </row>
@@ -8738,7 +9300,7 @@
       <c r="C101" t="s">
         <v>82</v>
       </c>
-      <c r="D101" s="72">
+      <c r="D101" s="55">
         <v>1191</v>
       </c>
     </row>
@@ -8752,7 +9314,7 @@
       <c r="C102" t="s">
         <v>81</v>
       </c>
-      <c r="D102" s="72">
+      <c r="D102" s="55">
         <v>1876</v>
       </c>
     </row>
@@ -8766,7 +9328,7 @@
       <c r="C103" t="s">
         <v>83</v>
       </c>
-      <c r="D103" s="72">
+      <c r="D103" s="55">
         <v>2327</v>
       </c>
     </row>
@@ -8780,7 +9342,7 @@
       <c r="C104" t="s">
         <v>84</v>
       </c>
-      <c r="D104" s="72">
+      <c r="D104" s="55">
         <v>1115</v>
       </c>
     </row>
@@ -8794,7 +9356,7 @@
       <c r="C105" t="s">
         <v>82</v>
       </c>
-      <c r="D105" s="72">
+      <c r="D105" s="55">
         <v>681</v>
       </c>
     </row>
@@ -8808,7 +9370,7 @@
       <c r="C106" t="s">
         <v>84</v>
       </c>
-      <c r="D106" s="72">
+      <c r="D106" s="55">
         <v>1000</v>
       </c>
     </row>
@@ -8822,7 +9384,7 @@
       <c r="C107" t="s">
         <v>82</v>
       </c>
-      <c r="D107" s="72">
+      <c r="D107" s="55">
         <v>1401</v>
       </c>
     </row>
@@ -8836,7 +9398,7 @@
       <c r="C108" t="s">
         <v>84</v>
       </c>
-      <c r="D108" s="72">
+      <c r="D108" s="55">
         <v>736</v>
       </c>
     </row>
@@ -8850,7 +9412,7 @@
       <c r="C109" t="s">
         <v>83</v>
       </c>
-      <c r="D109" s="72">
+      <c r="D109" s="55">
         <v>1761</v>
       </c>
     </row>
@@ -8864,7 +9426,7 @@
       <c r="C110" t="s">
         <v>84</v>
       </c>
-      <c r="D110" s="72">
+      <c r="D110" s="55">
         <v>872</v>
       </c>
     </row>
@@ -8878,7 +9440,7 @@
       <c r="C111" t="s">
         <v>82</v>
       </c>
-      <c r="D111" s="72">
+      <c r="D111" s="55">
         <v>2190</v>
       </c>
     </row>
@@ -8892,7 +9454,7 @@
       <c r="C112" t="s">
         <v>83</v>
       </c>
-      <c r="D112" s="72">
+      <c r="D112" s="55">
         <v>1212</v>
       </c>
     </row>
@@ -8906,7 +9468,7 @@
       <c r="C113" t="s">
         <v>82</v>
       </c>
-      <c r="D113" s="72">
+      <c r="D113" s="55">
         <v>2288</v>
       </c>
     </row>
@@ -8920,7 +9482,7 @@
       <c r="C114" t="s">
         <v>83</v>
       </c>
-      <c r="D114" s="72">
+      <c r="D114" s="55">
         <v>1905</v>
       </c>
     </row>
@@ -8934,7 +9496,7 @@
       <c r="C115" t="s">
         <v>81</v>
       </c>
-      <c r="D115" s="72">
+      <c r="D115" s="55">
         <v>525</v>
       </c>
     </row>
@@ -8948,7 +9510,7 @@
       <c r="C116" t="s">
         <v>83</v>
       </c>
-      <c r="D116" s="72">
+      <c r="D116" s="55">
         <v>1722</v>
       </c>
     </row>
@@ -8962,7 +9524,7 @@
       <c r="C117" t="s">
         <v>84</v>
       </c>
-      <c r="D117" s="72">
+      <c r="D117" s="55">
         <v>585</v>
       </c>
     </row>
@@ -8976,7 +9538,7 @@
       <c r="C118" t="s">
         <v>81</v>
       </c>
-      <c r="D118" s="72">
+      <c r="D118" s="55">
         <v>2497</v>
       </c>
     </row>
@@ -8990,7 +9552,7 @@
       <c r="C119" t="s">
         <v>82</v>
       </c>
-      <c r="D119" s="72">
+      <c r="D119" s="55">
         <v>465</v>
       </c>
     </row>
@@ -9004,7 +9566,7 @@
       <c r="C120" t="s">
         <v>83</v>
       </c>
-      <c r="D120" s="72">
+      <c r="D120" s="55">
         <v>2104</v>
       </c>
     </row>
@@ -9018,7 +9580,7 @@
       <c r="C121" t="s">
         <v>81</v>
       </c>
-      <c r="D121" s="72">
+      <c r="D121" s="55">
         <v>553</v>
       </c>
     </row>
@@ -9032,7 +9594,7 @@
       <c r="C122" t="s">
         <v>82</v>
       </c>
-      <c r="D122" s="72">
+      <c r="D122" s="55">
         <v>2088</v>
       </c>
     </row>
@@ -9046,7 +9608,7 @@
       <c r="C123" t="s">
         <v>84</v>
       </c>
-      <c r="D123" s="72">
+      <c r="D123" s="55">
         <v>56</v>
       </c>
     </row>
@@ -9060,7 +9622,7 @@
       <c r="C124" t="s">
         <v>81</v>
       </c>
-      <c r="D124" s="72">
+      <c r="D124" s="55">
         <v>1394</v>
       </c>
     </row>
@@ -9074,7 +9636,7 @@
       <c r="C125" t="s">
         <v>82</v>
       </c>
-      <c r="D125" s="72">
+      <c r="D125" s="55">
         <v>689</v>
       </c>
     </row>
@@ -9088,7 +9650,7 @@
       <c r="C126" t="s">
         <v>83</v>
       </c>
-      <c r="D126" s="72">
+      <c r="D126" s="55">
         <v>677</v>
       </c>
     </row>
@@ -9102,7 +9664,7 @@
       <c r="C127" t="s">
         <v>81</v>
       </c>
-      <c r="D127" s="72">
+      <c r="D127" s="55">
         <v>515</v>
       </c>
     </row>
@@ -9116,7 +9678,7 @@
       <c r="C128" t="s">
         <v>82</v>
       </c>
-      <c r="D128" s="72">
+      <c r="D128" s="55">
         <v>739</v>
       </c>
     </row>
@@ -9130,7 +9692,7 @@
       <c r="C129" t="s">
         <v>83</v>
       </c>
-      <c r="D129" s="72">
+      <c r="D129" s="55">
         <v>1353</v>
       </c>
     </row>
@@ -9144,7 +9706,7 @@
       <c r="C130" t="s">
         <v>82</v>
       </c>
-      <c r="D130" s="72">
+      <c r="D130" s="55">
         <v>756</v>
       </c>
     </row>
@@ -9158,7 +9720,7 @@
       <c r="C131" t="s">
         <v>82</v>
       </c>
-      <c r="D131" s="72">
+      <c r="D131" s="55">
         <v>60</v>
       </c>
     </row>
@@ -9172,7 +9734,7 @@
       <c r="C132" t="s">
         <v>84</v>
       </c>
-      <c r="D132" s="72">
+      <c r="D132" s="55">
         <v>1710</v>
       </c>
     </row>
@@ -9186,7 +9748,7 @@
       <c r="C133" t="s">
         <v>82</v>
       </c>
-      <c r="D133" s="72">
+      <c r="D133" s="55">
         <v>1783</v>
       </c>
     </row>
@@ -9200,7 +9762,7 @@
       <c r="C134" t="s">
         <v>84</v>
       </c>
-      <c r="D134" s="72">
+      <c r="D134" s="55">
         <v>1689</v>
       </c>
     </row>
@@ -9214,7 +9776,7 @@
       <c r="C135" t="s">
         <v>81</v>
       </c>
-      <c r="D135" s="72">
+      <c r="D135" s="55">
         <v>2352</v>
       </c>
     </row>
@@ -9228,7 +9790,7 @@
       <c r="C136" t="s">
         <v>82</v>
       </c>
-      <c r="D136" s="72">
+      <c r="D136" s="55">
         <v>2314</v>
       </c>
     </row>
@@ -9242,7 +9804,7 @@
       <c r="C137" t="s">
         <v>83</v>
       </c>
-      <c r="D137" s="72">
+      <c r="D137" s="55">
         <v>1363</v>
       </c>
     </row>
@@ -9256,7 +9818,7 @@
       <c r="C138" t="s">
         <v>81</v>
       </c>
-      <c r="D138" s="72">
+      <c r="D138" s="55">
         <v>143</v>
       </c>
     </row>
@@ -9270,7 +9832,7 @@
       <c r="C139" t="s">
         <v>83</v>
       </c>
-      <c r="D139" s="72">
+      <c r="D139" s="55">
         <v>667</v>
       </c>
     </row>
@@ -9284,7 +9846,7 @@
       <c r="C140" t="s">
         <v>84</v>
       </c>
-      <c r="D140" s="72">
+      <c r="D140" s="55">
         <v>71</v>
       </c>
     </row>
@@ -9298,7 +9860,7 @@
       <c r="C141" t="s">
         <v>81</v>
       </c>
-      <c r="D141" s="72">
+      <c r="D141" s="55">
         <v>1596</v>
       </c>
     </row>
@@ -9312,7 +9874,7 @@
       <c r="C142" t="s">
         <v>82</v>
       </c>
-      <c r="D142" s="72">
+      <c r="D142" s="55">
         <v>1496</v>
       </c>
     </row>
@@ -9326,7 +9888,7 @@
       <c r="C143" t="s">
         <v>81</v>
       </c>
-      <c r="D143" s="72">
+      <c r="D143" s="55">
         <v>1202</v>
       </c>
     </row>
@@ -9340,7 +9902,7 @@
       <c r="C144" t="s">
         <v>82</v>
       </c>
-      <c r="D144" s="72">
+      <c r="D144" s="55">
         <v>2322</v>
       </c>
     </row>
@@ -9354,7 +9916,7 @@
       <c r="C145" t="s">
         <v>84</v>
       </c>
-      <c r="D145" s="72">
+      <c r="D145" s="55">
         <v>1176</v>
       </c>
     </row>
@@ -9368,7 +9930,7 @@
       <c r="C146" t="s">
         <v>82</v>
       </c>
-      <c r="D146" s="72">
+      <c r="D146" s="55">
         <v>1921</v>
       </c>
     </row>
@@ -9382,7 +9944,7 @@
       <c r="C147" t="s">
         <v>84</v>
       </c>
-      <c r="D147" s="72">
+      <c r="D147" s="55">
         <v>764</v>
       </c>
     </row>
@@ -9396,7 +9958,7 @@
       <c r="C148" t="s">
         <v>81</v>
       </c>
-      <c r="D148" s="72">
+      <c r="D148" s="55">
         <v>698</v>
       </c>
     </row>
@@ -9410,7 +9972,7 @@
       <c r="C149" t="s">
         <v>82</v>
       </c>
-      <c r="D149" s="72">
+      <c r="D149" s="55">
         <v>484</v>
       </c>
     </row>
@@ -9424,7 +9986,7 @@
       <c r="C150" t="s">
         <v>83</v>
       </c>
-      <c r="D150" s="72">
+      <c r="D150" s="55">
         <v>1747</v>
       </c>
     </row>
@@ -9438,7 +10000,7 @@
       <c r="C151" t="s">
         <v>83</v>
       </c>
-      <c r="D151" s="72">
+      <c r="D151" s="55">
         <v>1484</v>
       </c>
     </row>
@@ -9452,7 +10014,7 @@
       <c r="C152" t="s">
         <v>81</v>
       </c>
-      <c r="D152" s="72">
+      <c r="D152" s="55">
         <v>1251</v>
       </c>
     </row>
@@ -9466,7 +10028,7 @@
       <c r="C153" t="s">
         <v>82</v>
       </c>
-      <c r="D153" s="72">
+      <c r="D153" s="55">
         <v>763</v>
       </c>
     </row>
@@ -9480,7 +10042,7 @@
       <c r="C154" t="s">
         <v>84</v>
       </c>
-      <c r="D154" s="72">
+      <c r="D154" s="55">
         <v>2026</v>
       </c>
     </row>
@@ -9494,7 +10056,7 @@
       <c r="C155" t="s">
         <v>83</v>
       </c>
-      <c r="D155" s="72">
+      <c r="D155" s="55">
         <v>968</v>
       </c>
     </row>
@@ -9508,7 +10070,7 @@
       <c r="C156" t="s">
         <v>84</v>
       </c>
-      <c r="D156" s="72">
+      <c r="D156" s="55">
         <v>2138</v>
       </c>
     </row>
@@ -9522,7 +10084,7 @@
       <c r="C157" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="72">
+      <c r="D157" s="55">
         <v>2186</v>
       </c>
     </row>
@@ -9536,7 +10098,7 @@
       <c r="C158" t="s">
         <v>83</v>
       </c>
-      <c r="D158" s="72">
+      <c r="D158" s="55">
         <v>287</v>
       </c>
     </row>
@@ -9550,7 +10112,7 @@
       <c r="C159" t="s">
         <v>81</v>
       </c>
-      <c r="D159" s="72">
+      <c r="D159" s="55">
         <v>552</v>
       </c>
     </row>
@@ -9564,7 +10126,7 @@
       <c r="C160" t="s">
         <v>82</v>
       </c>
-      <c r="D160" s="72">
+      <c r="D160" s="55">
         <v>2260</v>
       </c>
     </row>
@@ -9578,7 +10140,7 @@
       <c r="C161" t="s">
         <v>83</v>
       </c>
-      <c r="D161" s="72">
+      <c r="D161" s="55">
         <v>899</v>
       </c>
     </row>
@@ -9592,7 +10154,7 @@
       <c r="C162" t="s">
         <v>82</v>
       </c>
-      <c r="D162" s="72">
+      <c r="D162" s="55">
         <v>413</v>
       </c>
     </row>
@@ -9606,7 +10168,7 @@
       <c r="C163" t="s">
         <v>83</v>
       </c>
-      <c r="D163" s="72">
+      <c r="D163" s="55">
         <v>2191</v>
       </c>
     </row>
@@ -9620,7 +10182,7 @@
       <c r="C164" t="s">
         <v>84</v>
       </c>
-      <c r="D164" s="72">
+      <c r="D164" s="55">
         <v>947</v>
       </c>
     </row>
@@ -9634,7 +10196,7 @@
       <c r="C165" t="s">
         <v>82</v>
       </c>
-      <c r="D165" s="72">
+      <c r="D165" s="55">
         <v>1990</v>
       </c>
     </row>
@@ -9648,7 +10210,7 @@
       <c r="C166" t="s">
         <v>84</v>
       </c>
-      <c r="D166" s="72">
+      <c r="D166" s="55">
         <v>1998</v>
       </c>
     </row>
@@ -9662,7 +10224,7 @@
       <c r="C167" t="s">
         <v>81</v>
       </c>
-      <c r="D167" s="72">
+      <c r="D167" s="55">
         <v>490</v>
       </c>
     </row>
@@ -9676,7 +10238,7 @@
       <c r="C168" t="s">
         <v>82</v>
       </c>
-      <c r="D168" s="72">
+      <c r="D168" s="55">
         <v>964</v>
       </c>
     </row>
@@ -9690,7 +10252,7 @@
       <c r="C169" t="s">
         <v>83</v>
       </c>
-      <c r="D169" s="72">
+      <c r="D169" s="55">
         <v>332</v>
       </c>
     </row>
@@ -9704,7 +10266,7 @@
       <c r="C170" t="s">
         <v>83</v>
       </c>
-      <c r="D170" s="72">
+      <c r="D170" s="55">
         <v>783</v>
       </c>
     </row>
@@ -9718,7 +10280,7 @@
       <c r="C171" t="s">
         <v>84</v>
       </c>
-      <c r="D171" s="72">
+      <c r="D171" s="55">
         <v>2538</v>
       </c>
     </row>
@@ -9732,7 +10294,7 @@
       <c r="C172" t="s">
         <v>81</v>
       </c>
-      <c r="D172" s="72">
+      <c r="D172" s="55">
         <v>2165</v>
       </c>
     </row>
@@ -9746,7 +10308,7 @@
       <c r="C173" t="s">
         <v>84</v>
       </c>
-      <c r="D173" s="72">
+      <c r="D173" s="55">
         <v>2087</v>
       </c>
     </row>
@@ -9760,7 +10322,7 @@
       <c r="C174" t="s">
         <v>81</v>
       </c>
-      <c r="D174" s="72">
+      <c r="D174" s="55">
         <v>2599</v>
       </c>
     </row>
@@ -9774,7 +10336,7 @@
       <c r="C175" t="s">
         <v>83</v>
       </c>
-      <c r="D175" s="72">
+      <c r="D175" s="55">
         <v>495</v>
       </c>
     </row>
@@ -9788,7 +10350,7 @@
       <c r="C176" t="s">
         <v>84</v>
       </c>
-      <c r="D176" s="72">
+      <c r="D176" s="55">
         <v>805</v>
       </c>
     </row>
@@ -9802,7 +10364,7 @@
       <c r="C177" t="s">
         <v>84</v>
       </c>
-      <c r="D177" s="72">
+      <c r="D177" s="55">
         <v>1837</v>
       </c>
     </row>
@@ -9816,7 +10378,7 @@
       <c r="C178" t="s">
         <v>81</v>
       </c>
-      <c r="D178" s="72">
+      <c r="D178" s="55">
         <v>758</v>
       </c>
     </row>
@@ -9830,7 +10392,7 @@
       <c r="C179" t="s">
         <v>82</v>
       </c>
-      <c r="D179" s="72">
+      <c r="D179" s="55">
         <v>955</v>
       </c>
     </row>
@@ -9844,7 +10406,7 @@
       <c r="C180" t="s">
         <v>83</v>
       </c>
-      <c r="D180" s="72">
+      <c r="D180" s="55">
         <v>584</v>
       </c>
     </row>
@@ -9858,7 +10420,7 @@
       <c r="C181" t="s">
         <v>84</v>
       </c>
-      <c r="D181" s="72">
+      <c r="D181" s="55">
         <v>450</v>
       </c>
     </row>
@@ -9872,7 +10434,7 @@
       <c r="C182" t="s">
         <v>81</v>
       </c>
-      <c r="D182" s="72">
+      <c r="D182" s="55">
         <v>1571</v>
       </c>
     </row>
@@ -9886,7 +10448,7 @@
       <c r="C183" t="s">
         <v>82</v>
       </c>
-      <c r="D183" s="72">
+      <c r="D183" s="55">
         <v>255</v>
       </c>
     </row>
@@ -9900,7 +10462,7 @@
       <c r="C184" t="s">
         <v>83</v>
       </c>
-      <c r="D184" s="72">
+      <c r="D184" s="55">
         <v>2099</v>
       </c>
     </row>
@@ -9914,7 +10476,7 @@
       <c r="C185" t="s">
         <v>84</v>
       </c>
-      <c r="D185" s="72">
+      <c r="D185" s="55">
         <v>1393</v>
       </c>
     </row>
@@ -9941,7 +10503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF898781"/>
@@ -11025,7 +11587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF898781"/>
@@ -11053,7 +11615,7 @@
       </c>
       <c r="B2" s="2">
         <f ca="1">TODAY()</f>
-        <v>46221</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -11508,7 +12070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF898781"/>
